--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486795_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486795_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5267</v>
+        <v>6.582</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9241</v>
+        <v>4.4761</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6026</v>
+        <v>2.106</v>
       </c>
       <c r="G2" t="n">
         <v>2.9624</v>
@@ -610,13 +610,13 @@
         <v>2.7031</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5723</v>
+        <v>0.6276</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8818</v>
+        <v>0.4338</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6904</v>
+        <v>0.1938</v>
       </c>
       <c r="V2" t="n">
         <v>2.4128</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. VILLALBA BAULBYS</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2139</v>
+        <v>2.5635</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2646</v>
+        <v>1.9226</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0507</v>
+        <v>0.6409</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6226</v>
+        <v>1.7291</v>
       </c>
       <c r="H3" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.4672</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.1365</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.9518</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.1846</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.4074</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.6899</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.1585</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.4641</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.6582</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.4006</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3.2577</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-0.0357</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.7579</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-0.7935</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.7723</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.1931</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2744</v>
+        <v>-0.3241</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7995</v>
+        <v>-0.0208</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4749</v>
+        <v>-0.3033</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>M. VILLALBA BAULBYS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.017</v>
+        <v>2.4499</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5465</v>
+        <v>3.6993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4705</v>
+        <v>-1.2494</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7592</v>
+        <v>3.6226</v>
       </c>
       <c r="H4" t="n">
-        <v>0.696</v>
+        <v>1.1585</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0633</v>
+        <v>2.4641</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5676</v>
+        <v>3.6582</v>
       </c>
       <c r="K4" t="n">
-        <v>0.49</v>
+        <v>0.4006</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0776</v>
+        <v>3.2577</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8083</v>
+        <v>-0.0357</v>
       </c>
       <c r="N4" t="n">
-        <v>0.206</v>
+        <v>0.7579</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0143</v>
+        <v>-0.7935</v>
       </c>
       <c r="P4" t="n">
         <v>0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.171</v>
+        <v>0.5104</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0557</v>
+        <v>0.2341</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1153</v>
+        <v>0.2763</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6565</v>
+        <v>-2.4554</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6565</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8283</v>
+        <v>2.0847</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3364</v>
+        <v>1.6638</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4919</v>
+        <v>0.4208</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7291</v>
+        <v>0.7592</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2619</v>
+        <v>0.696</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4672</v>
+        <v>0.0633</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1365</v>
+        <v>2.5676</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9518</v>
+        <v>0.49</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1846</v>
+        <v>2.0776</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4074</v>
+        <v>-1.8083</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6899</v>
+        <v>0.206</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2826</v>
+        <v>-2.0143</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3515</v>
+        <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0593</v>
+        <v>-0.1034</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.607</v>
+        <v>0.0616</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4523</v>
+        <v>-0.165</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.751</v>
+        <v>1.1222</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3395</v>
+        <v>0.512</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4116</v>
+        <v>0.6102</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9221</v>
@@ -922,13 +922,13 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6125</v>
+        <v>-0.2413</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1934</v>
+        <v>-0.0209</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.419</v>
+        <v>-0.2204</v>
       </c>
       <c r="V6" t="n">
         <v>1.5133</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0697</v>
+        <v>0.9399</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1069</v>
+        <v>-0.3208</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0372</v>
+        <v>1.2607</v>
       </c>
       <c r="G7" t="n">
         <v>1.2069</v>
@@ -1000,13 +1000,13 @@
         <v>2.51</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2027</v>
+        <v>-0.1931</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8555</v>
+        <v>-0.0694</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3472</v>
+        <v>-0.1237</v>
       </c>
       <c r="V7" t="n">
         <v>1.4707</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4759</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2579</v>
+        <v>0.3683</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7338</v>
+        <v>-0.4359</v>
       </c>
       <c r="G8" t="n">
         <v>0.2223</v>
@@ -1078,13 +1078,13 @@
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.629</v>
+        <v>-0.2206</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3314</v>
+        <v>-0.2211</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2975</v>
+        <v>0.0005</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7169</v>
+        <v>-3.6342</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.082</v>
+        <v>-2.8751</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6349</v>
+        <v>-0.7591</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9997</v>
@@ -1156,13 +1156,13 @@
         <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.138</v>
+        <v>-0.0553</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3312</v>
+        <v>-0.1244</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1933</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7533</v>
+        <v>-4.0638</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9318</v>
+        <v>-4.2422</v>
       </c>
       <c r="F10" t="n">
         <v>0.1785</v>
@@ -1234,10 +1234,10 @@
         <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1034</v>
+        <v>-0.4138</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8279</v>
+        <v>-0.1383</v>
       </c>
       <c r="U10" t="n">
         <v>-0.2756</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.3211</v>
+        <v>7.9766</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5483</v>
+        <v>5.204000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>2.772899999999999</v>
+        <v>2.7727</v>
       </c>
       <c r="G11" t="n">
         <v>-0.03460000000000019</v>
@@ -1285,13 +1285,13 @@
         <v>-0.03389999999999938</v>
       </c>
       <c r="J11" t="n">
-        <v>6.561999999999999</v>
+        <v>6.561999999999998</v>
       </c>
       <c r="K11" t="n">
         <v>-0.6838999999999995</v>
       </c>
       <c r="L11" t="n">
-        <v>7.245899999999999</v>
+        <v>7.245900000000001</v>
       </c>
       <c r="M11" t="n">
         <v>-6.596599999999999</v>
@@ -1312,10 +1312,10 @@
         <v>13.5155</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0692</v>
+        <v>-0.4135999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5208</v>
+        <v>0.1346000000000001</v>
       </c>
       <c r="U11" t="n">
         <v>-0.5483</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.0416</v>
+        <v>5.869</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0637</v>
+        <v>4.4774</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9779</v>
+        <v>1.3916</v>
       </c>
       <c r="G12" t="n">
         <v>4.222</v>
@@ -1390,13 +1390,13 @@
         <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3309</v>
+        <v>0.4965</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.1937</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2765</v>
+        <v>0.6902</v>
       </c>
       <c r="V12" t="n">
         <v>0.5712</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9679</v>
+        <v>2.0397</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4973</v>
+        <v>0.5665</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4706</v>
+        <v>1.4732</v>
       </c>
       <c r="G13" t="n">
         <v>2.6313</v>
@@ -1468,13 +1468,13 @@
         <v>1.3515</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1901</v>
+        <v>1.262</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4613</v>
+        <v>0.5305</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7288</v>
+        <v>0.7315</v>
       </c>
       <c r="V13" t="n">
         <v>0.6565</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6549</v>
+        <v>1.961</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5531</v>
+        <v>0.76</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1018</v>
+        <v>1.2011</v>
       </c>
       <c r="G14" t="n">
         <v>1.1253</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1269</v>
+        <v>0.1793</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2207</v>
+        <v>-0.0139</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0939</v>
+        <v>0.1932</v>
       </c>
       <c r="V14" t="n">
         <v>0.6565</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4131</v>
+        <v>1.3164</v>
       </c>
       <c r="E15" t="n">
         <v>0.0062</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4069</v>
+        <v>1.3102</v>
       </c>
       <c r="G15" t="n">
         <v>0.8888</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5243</v>
+        <v>0.4277</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5795</v>
+        <v>0.4828</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>M. LOZANO MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.1379</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9256</v>
+        <v>-0.0552</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0254</v>
+        <v>0.1931</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4011</v>
+        <v>0.1379</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2346</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1665</v>
+        <v>0.1379</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1744</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0281</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1462</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2268</v>
+        <v>0.1379</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2065</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0203</v>
+        <v>0.1379</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3515</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1292</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.682</v>
+        <v>-0.0552</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4472</v>
+        <v>0.0552</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. LOZANO MARTINEZ</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1379</v>
+        <v>-0.0335</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0552</v>
+        <v>-0.1086</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1931</v>
+        <v>0.0751</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1379</v>
+        <v>1.4011</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.2346</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1379</v>
+        <v>1.1665</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.1744</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0281</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.1462</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1379</v>
+        <v>0.2268</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.2065</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1379</v>
+        <v>0.0203</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.1446</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0552</v>
+        <v>0.6478</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0552</v>
+        <v>0.4968</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0422</v>
+        <v>-0.067</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4182</v>
+        <v>0.7277</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4604</v>
+        <v>-0.7947</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4309</v>
+        <v>-1.3525</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8069</v>
+        <v>-0.9863</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.376</v>
+        <v>-0.3662</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2666</v>
+        <v>0.3113</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2213</v>
+        <v>-0.9163</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0453</v>
+        <v>1.2276</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8357</v>
+        <v>-1.6638</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4145</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.4212</v>
+        <v>-1.5939</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7723</v>
+        <v>0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1585</v>
+        <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1987</v>
+        <v>0.2276</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0824</v>
+        <v>-0.1315</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1163</v>
+        <v>0.3591</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8995</v>
+        <v>0.2856</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8995</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4033</v>
+        <v>-1.2064</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0037</v>
+        <v>1.3148</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4071</v>
+        <v>-2.5212</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3525</v>
+        <v>0.4309</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9863</v>
+        <v>2.8069</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3662</v>
+        <v>-2.376</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3113</v>
+        <v>3.2666</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9163</v>
+        <v>3.2213</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2276</v>
+        <v>0.0453</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6638</v>
+        <v>-2.8357</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.4145</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5939</v>
+        <v>-2.4212</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7723</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7377</v>
+        <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1087</v>
+        <v>0.0345</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8555</v>
+        <v>-0.0211</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2532</v>
+        <v>0.0555</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2856</v>
+        <v>-0.8995</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2277</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6914</v>
+        <v>-2.3482</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3717</v>
+        <v>-2.7512</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3197</v>
+        <v>0.403</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6831</v>
@@ -2014,13 +2014,13 @@
         <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9157999999999999</v>
+        <v>0.4275</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4416</v>
+        <v>0.179</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4742</v>
+        <v>0.2486</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2856</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5568</v>
+        <v>-4.7996</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4265</v>
+        <v>-2.6333</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1303</v>
+        <v>-2.1663</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1857</v>
@@ -2092,13 +2092,13 @@
         <v>0.3862</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4358</v>
+        <v>0.193</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1652</v>
+        <v>-0.0417</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2706</v>
+        <v>0.2347</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.7938</v>
+        <v>-7.1222</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3873</v>
+        <v>-5.077</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4065</v>
+        <v>-2.0451</v>
       </c>
       <c r="G22" t="n">
         <v>-3.5813</v>
@@ -2170,13 +2170,13 @@
         <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.2552</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6071</v>
+        <v>-0.2969</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3198</v>
+        <v>0.0416</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1271</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.321000000000002</v>
+        <v>-4.252900000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.772899999999999</v>
+        <v>-2.772699999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.548299999999999</v>
+        <v>-1.48</v>
       </c>
       <c r="G23" t="n">
         <v>0.03469999999999995</v>
@@ -2248,13 +2248,13 @@
         <v>8.688499999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>2.0689</v>
+        <v>4.137499999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5482</v>
+        <v>0.5481</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5208</v>
+        <v>3.5892</v>
       </c>
       <c r="V23" t="n">
         <v>-3.5978</v>
